--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
+    <t>شاى ليبتون ناعم  - 250 جم</t>
+  </si>
+  <si>
+    <t>ستينج فراولة زجاج - 275 مل</t>
+  </si>
+  <si>
     <t>كوكا كولا - 2.45 لتر</t>
-  </si>
-  <si>
-    <t>كوكاكولا اكشن - 300 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,36 +432,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2778</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>217.5</v>
+        <v>2496</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>6935</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>1124</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>108</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D4">
+        <v>157</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>2778</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>210</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شاى ليبتون ناعم  - 250 جم</t>
-  </si>
-  <si>
-    <t>ستينج فراولة زجاج - 275 مل</t>
-  </si>
-  <si>
-    <t>كوكا كولا - 2.45 لتر</t>
+    <t>هارفست صلصة شرينك ٢ برطمان خصم   15 % --- 320 جم</t>
+  </si>
+  <si>
+    <t>عسل اسود الرشيدى الميزان بلاستيك - 650 جم</t>
+  </si>
+  <si>
+    <t>شاى الكبوس - 100 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,16 +432,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>88</v>
+        <v>5080</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2496</v>
+        <v>249.25</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -449,16 +449,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>88</v>
+        <v>6360</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>52</v>
+        <v>41.25</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -466,16 +466,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1124</v>
+        <v>6360</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>157</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -483,18 +483,35 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2778</v>
+        <v>10093</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>210</v>
+        <v>2130</v>
       </c>
       <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>10093</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>35.5</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
+    <t>لبن بخيره - 500 مل</t>
+  </si>
+  <si>
     <t>هارفست صلصة شرينك ٢ برطمان خصم   15 % --- 320 جم</t>
   </si>
   <si>
-    <t>عسل اسود الرشيدى الميزان بلاستيك - 650 جم</t>
-  </si>
-  <si>
-    <t>شاى الكبوس - 100 جرام</t>
+    <t>كاتشب هاينز اسكويزى دوى باك - 125 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,16 +432,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5080</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>249.25</v>
+        <v>500</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -449,16 +449,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>6360</v>
+        <v>5080</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>41.25</v>
+        <v>253.5</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -466,52 +466,18 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>6360</v>
+        <v>9690</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>495</v>
+        <v>392</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>10093</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2130</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>10093</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>35.5</v>
-      </c>
-      <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لبن بخيره - 500 مل</t>
-  </si>
-  <si>
-    <t>هارفست صلصة شرينك ٢ برطمان خصم   15 % --- 320 جم</t>
-  </si>
-  <si>
-    <t>كاتشب هاينز اسكويزى دوى باك - 125 جم</t>
+    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة طويل جدا بالالوفيرا + 2 مجانا - 14 فوطة</t>
   </si>
   <si>
     <t>YES</t>
@@ -432,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>130</v>
+        <v>5976</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -441,44 +438,44 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>500</v>
+        <v>182.25</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>5080</v>
+        <v>12979</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>253.5</v>
+        <v>45.25</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>9690</v>
+        <v>12979</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>392</v>
+        <v>724</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
-  </si>
-  <si>
-    <t>اولويز ماكسى سميكة طويل جدا بالالوفيرا + 2 مجانا - 14 فوطة</t>
+    <t>عصير بيتى برتقال - 235 مل</t>
+  </si>
+  <si>
+    <t>ارز حبوبة عريض الحبة - 1 كجم</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>أولويز ماكسى سميكة ناعمة حساس بلمسة الألوڤيرا طويلة جدا- + 2 فوطة مجانا 14 فوطة</t>
+  </si>
+  <si>
+    <t>مسحوق ليدر اتوماتيك جردل لافندر (1ك زيادة) - 5 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +438,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5976</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>182.25</v>
+        <v>189.25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>12979</v>
+        <v>1243</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>45.25</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>12979</v>
+        <v>6494</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>724</v>
+        <v>580.5</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>9841</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>596</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>9841</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>37.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>10181</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>218.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,28 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>عصير بيتى برتقال - 235 مل</t>
-  </si>
-  <si>
-    <t>ارز حبوبة عريض الحبة - 1 كجم</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>أولويز ماكسى سميكة ناعمة حساس بلمسة الألوڤيرا طويلة جدا- + 2 فوطة مجانا 14 فوطة</t>
-  </si>
-  <si>
-    <t>مسحوق ليدر اتوماتيك جردل لافندر (1ك زيادة) - 5 كجم</t>
+    <t>مرقة ماجى دجاج شريط - 8 جم</t>
+  </si>
+  <si>
+    <t>طحينة البوادى - 240 جم</t>
+  </si>
+  <si>
+    <t>ريحانة عدس بحبه- 500 جم</t>
+  </si>
+  <si>
+    <t>مكرونة خطيرة شعرية - 280 جم</t>
+  </si>
+  <si>
+    <t>لبان كلورتس قرفة و ليمون بالنعناع - 1 جنية</t>
+  </si>
+  <si>
+    <t>اوكسى جل بلاك - 185 جم</t>
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -410,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,104 +444,206 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>189.25</v>
+        <v>747</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1243</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>294</v>
+        <v>41.5</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>6494</v>
+        <v>590</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>580.5</v>
+        <v>600</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>9841</v>
+        <v>590</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5">
-        <v>596</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>9841</v>
+        <v>590</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>37.25</v>
+        <v>300</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>10181</v>
+        <v>590</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1200</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>2265</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>815</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>2265</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>40.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>5869</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>136</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>10514</v>
+      </c>
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>218.5</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1700</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>10514</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11271</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>93.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>هارفست فول مقشور بالصلصه خصم %15 - 400 جم</t>
+    <t>سبرايت - 0.95 لتر</t>
+  </si>
+  <si>
+    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,36 +429,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>10448</v>
+        <v>3674</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>16.75</v>
+        <v>122.75</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>10448</v>
+        <v>3934</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>201</v>
+        <v>52.5</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,70 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سبرايت - 0.95 لتر</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
+    <t>شويبس يوسفى جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>شويبس يوسفى - 950 مل</t>
+  </si>
+  <si>
+    <t>شويبس جولد خوخ - 950 مل</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +489,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3674</v>
+        <v>6931</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,27 +498,469 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>122.75</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3934</v>
+        <v>8649</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>52.5</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>8651</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>160</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21704</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>693</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21704</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>19.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21705</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>870</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21705</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>36.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21706</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>26.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21706</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>963</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21707</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1272</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21707</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21709</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1132.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21709</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>37.75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21713</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>630</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21713</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>26.25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21745</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>417.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21752</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>474.25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21754</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>417.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21771</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>417.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>21773</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>368.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21774</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>474.25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21777</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>368.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>21781</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>283</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>21783</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>356.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>21789</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>310</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>22125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>474.25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>22126</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>368.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>25775</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>280</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,70 +37,64 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس يوسفى جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>شويبس يوسفى - 950 مل</t>
-  </si>
-  <si>
-    <t>شويبس جولد خوخ - 950 مل</t>
-  </si>
-  <si>
-    <t>باندا مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>باندا مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
-  </si>
-  <si>
-    <t>ديرى مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا  - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا  - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 250 جرام</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 125 جرام</t>
-  </si>
-  <si>
-    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت هدية خليط- 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس - 5 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -461,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -489,58 +483,58 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6931</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>285</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>8649</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>160</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>8651</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>160</v>
+        <v>863.5</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21704</v>
+        <v>479</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -549,418 +543,282 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>693</v>
+        <v>878.75</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21704</v>
+        <v>922</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>19.25</v>
+        <v>612</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21705</v>
+        <v>1490</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>870</v>
+        <v>604</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21705</v>
+        <v>1492</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>36.25</v>
+        <v>860</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21706</v>
+        <v>2608</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>26.75</v>
+        <v>725.25</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21706</v>
+        <v>2878</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>963</v>
+        <v>388.25</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21707</v>
+        <v>2879</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1272</v>
+        <v>810</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21707</v>
+        <v>2916</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>53</v>
+        <v>955</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21709</v>
+        <v>2935</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>1132.5</v>
+        <v>892.5</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21709</v>
+        <v>6497</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>37.75</v>
+        <v>855</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21713</v>
+        <v>7324</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>630</v>
+        <v>480.5</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21713</v>
+        <v>9070</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>26.25</v>
+        <v>895</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21745</v>
+        <v>11961</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>417.5</v>
+        <v>533.25</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21752</v>
+        <v>11962</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>474.25</v>
+        <v>681.75</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21754</v>
+        <v>12923</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>417.5</v>
+        <v>855</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21771</v>
+        <v>12924</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>417.5</v>
+        <v>600</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21773</v>
+        <v>12925</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>368.5</v>
+        <v>490</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21774</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>474.25</v>
-      </c>
-      <c r="E22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21777</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>368.5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21781</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>283</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21783</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>356.5</v>
-      </c>
-      <c r="E25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21789</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>310</v>
-      </c>
-      <c r="E26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22125</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>474.25</v>
-      </c>
-      <c r="E27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22126</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>368.5</v>
-      </c>
-      <c r="E28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>25775</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>280</v>
-      </c>
-      <c r="E29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,64 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت هدية خليط- 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 700 مل</t>
+    <t>زيت حبوبة خليط - 900 مل</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 700 مل</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -455,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -483,7 +435,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>823</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -492,15 +444,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>1490</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -509,15 +461,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>470</v>
+        <v>6496</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -526,299 +478,27 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>863.5</v>
+        <v>772</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>479</v>
+        <v>19981</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>878.75</v>
+        <v>460</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>922</v>
-      </c>
-      <c r="B6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>612</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1490</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>604</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>1492</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>860</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>2608</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>725.25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>2878</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>388.25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>2879</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>810</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>2916</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>955</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>2935</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>892.5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>6497</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>855</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>7324</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>480.5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>9070</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>895</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11961</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>533.25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>11962</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>681.75</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>12923</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>855</v>
-      </c>
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>12924</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>600</v>
-      </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>12925</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>490</v>
-      </c>
-      <c r="E21" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+    <t>دومتي عصير مانجو- 1 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,70 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>823</v>
+        <v>3865</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>1490</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>620</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>6496</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>772</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19981</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>460</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1125.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>دومتي عصير مانجو- 1 لتر</t>
+    <t>شويبس جولد خوخ - 300 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3865</v>
+        <v>1655</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
